--- a/russian_data/processed/DATASET-rub.xlsx
+++ b/russian_data/processed/DATASET-rub.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,39 +433,39 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>delta_non_rus</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ret_t</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rpo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IGREA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rub_diff</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -473,7 +485,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -493,7 +505,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -513,7 +525,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -533,7 +545,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -553,7 +565,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -593,7 +605,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -653,7 +665,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -693,7 +705,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -713,7 +725,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -753,7 +765,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -773,7 +785,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -793,7 +805,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -813,7 +825,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -833,7 +845,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -853,7 +865,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -873,7 +885,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -893,7 +905,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -913,7 +925,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -933,7 +945,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -953,7 +965,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -973,7 +985,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -993,7 +1005,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1013,7 +1025,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1053,7 +1065,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1073,7 +1085,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1093,7 +1105,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -1113,7 +1125,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -1133,7 +1145,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -1153,7 +1165,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -1213,7 +1225,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -1233,7 +1245,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -1253,7 +1265,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -1273,7 +1285,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -1293,7 +1305,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -1353,7 +1365,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -1373,7 +1385,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -1393,7 +1405,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -1413,7 +1425,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -1433,7 +1445,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -1453,7 +1465,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -1473,7 +1485,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -1493,7 +1505,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -1513,7 +1525,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -1533,7 +1545,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -1553,7 +1565,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -1573,7 +1585,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -1593,7 +1605,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -1613,7 +1625,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -1633,7 +1645,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -1653,7 +1665,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -1713,7 +1725,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -1733,7 +1745,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -1793,7 +1805,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -1833,7 +1845,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -1853,7 +1865,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -1873,7 +1885,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -1893,7 +1905,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -1913,7 +1925,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -1933,7 +1945,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -1953,7 +1965,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -1973,7 +1985,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -1993,7 +2005,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2013,7 +2025,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2053,7 +2065,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2073,7 +2085,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2093,7 +2105,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2113,7 +2125,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
